--- a/curation_benchmark/results/supp_tables/supp_table_MWU.xlsx
+++ b/curation_benchmark/results/supp_tables/supp_table_MWU.xlsx
@@ -17,18 +17,16 @@
     <sheet name="Cancer_MSK (80%)" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Cancer_TCGA (80%)" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Cancer_AlphaMissense (80%)" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ClinVar_Balanced (80%)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="ADRD (90%)" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="ASD (90%)" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="ASD_excl_ClinVar (90%)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="CHD (90%)" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="CHD_excl_ClinVar (90%)" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="DDD (90%)" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="DDD_excl_ClinVar (90%)" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Cancer_MSK (90%)" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Cancer_TCGA (90%)" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Cancer_AlphaMissense (90%)" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="ClinVar_Balanced (90%)" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="ADRD (90%)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="ASD (90%)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ASD_excl_ClinVar (90%)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="CHD (90%)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="CHD_excl_ClinVar (90%)" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="DDD (90%)" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="DDD_excl_ClinVar (90%)" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Cancer_MSK (90%)" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Cancer_TCGA (90%)" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Cancer_AlphaMissense (90%)" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1858,7 +1856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1890,653 +1888,382 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B2" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C2" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AlphaMissense</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>BayesDel_addAF</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>57.26200882217539</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B3" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C3" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BayesDel_addAF</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>ClinPred</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>57.08448921640914</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B4" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C4" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BayesDel_noAF</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>MetaRNN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>54.78952627752447</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B5" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C5" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ClinPred</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>AlphaMissense</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>51.4324843221459</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B6" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C6" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DANN</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>VEST4</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>51.42297276551336</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B7" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C7" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DEOGEN2</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>BayesDel_noAF</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>48.60237961613969</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B8" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C8" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ESM1b</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>DEOGEN2</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>47.8052457806591</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B9" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C9" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>fathmm-XF_coding</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>REVEL</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>47.58943960402964</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B10" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C10" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>gMVP</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Eigen-raw_coding</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>43.22042540958235</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B11" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C11" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>fathmm-XF_coding</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>42.80940516774943</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B12" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C12" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>M-CAP</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Eigen-PC-raw_coding</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>42.59311878423031</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B13" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C13" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>MetaLR</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="E13" t="n">
+        <v>41.80143635914721</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B14" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C14" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MetaRNN</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>PROVEAN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>38.98051171300805</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B15" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C15" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MetaSVM</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Polyphen2_HVAR</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>36.18331921105626</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B16" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C16" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MutationAssessor</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Polyphen2_HDIV</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>33.7954747110272</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B17" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C17" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MutFormer</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>CADD_raw</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>30.8313569105263</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B18" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C18" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MutScore</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>MetaSVM</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>28.92731404548947</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B19" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C19" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>SIFT4G</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>27.50314752751326</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B20" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C20" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PHACTboost</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>SIFT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>26.55242447380517</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>24248</v>
+        <v>553</v>
       </c>
       <c r="B21" t="n">
-        <v>14704</v>
+        <v>427</v>
       </c>
       <c r="C21" t="n">
-        <v>9544</v>
+        <v>126</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>24248</v>
-      </c>
-      <c r="B22" t="n">
-        <v>14704</v>
-      </c>
-      <c r="C22" t="n">
-        <v>9544</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Polyphen2_HVAR</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>24248</v>
-      </c>
-      <c r="B23" t="n">
-        <v>14704</v>
-      </c>
-      <c r="C23" t="n">
-        <v>9544</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>PrimateAI</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>24248</v>
-      </c>
-      <c r="B24" t="n">
-        <v>14704</v>
-      </c>
-      <c r="C24" t="n">
-        <v>9544</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>PROVEAN</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24248</v>
-      </c>
-      <c r="B25" t="n">
-        <v>14704</v>
-      </c>
-      <c r="C25" t="n">
-        <v>9544</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>REVEL</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>24248</v>
-      </c>
-      <c r="B26" t="n">
-        <v>14704</v>
-      </c>
-      <c r="C26" t="n">
-        <v>9544</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>SIFT</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24248</v>
-      </c>
-      <c r="B27" t="n">
-        <v>14704</v>
-      </c>
-      <c r="C27" t="n">
-        <v>9544</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>SIFT4G</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>24248</v>
-      </c>
-      <c r="B28" t="n">
-        <v>14704</v>
-      </c>
-      <c r="C28" t="n">
-        <v>9544</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>VARITY_ER</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>24248</v>
-      </c>
-      <c r="B29" t="n">
-        <v>14704</v>
-      </c>
-      <c r="C29" t="n">
-        <v>9544</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>VARITY_ER_LOO</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>24248</v>
-      </c>
-      <c r="B30" t="n">
-        <v>14704</v>
-      </c>
-      <c r="C30" t="n">
-        <v>9544</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>VARITY_R</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>24248</v>
-      </c>
-      <c r="B31" t="n">
-        <v>14704</v>
-      </c>
-      <c r="C31" t="n">
-        <v>9544</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>VARITY_R_LOO</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>24248</v>
-      </c>
-      <c r="B32" t="n">
-        <v>14704</v>
-      </c>
-      <c r="C32" t="n">
-        <v>9544</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>VEST4</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>DANN</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>17.6167952865155</v>
       </c>
     </row>
   </sheetData>
@@ -2550,7 +2277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2582,382 +2309,629 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B2" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C2" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BayesDel_addAF</t>
+          <t>MutFormer</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>57.26200882217539</v>
+        <v>4.671893869503933</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B3" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C3" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ClinPred</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>57.08448921640914</v>
+        <v>4.46492974877247</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B4" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C4" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MetaRNN</t>
+          <t>BayesDel_noAF</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>54.78952627752447</v>
+        <v>4.276840084145703</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B5" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C5" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AlphaMissense</t>
+          <t>Eigen-raw_coding</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>51.4324843221459</v>
+        <v>4.192636285038138</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B6" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C6" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VEST4</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>51.42297276551336</v>
+        <v>4.087919008248451</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B7" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C7" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BayesDel_noAF</t>
+          <t>MetaRNN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>48.60237961613969</v>
+        <v>3.803459535838075</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B8" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C8" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DEOGEN2</t>
+          <t>BayesDel_addAF</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>47.8052457806591</v>
+        <v>3.681327619798411</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B9" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C9" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>REVEL</t>
+          <t>PHACTboost</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47.58943960402964</v>
+        <v>3.586334924503044</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B10" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C10" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Eigen-raw_coding</t>
+          <t>PrimateAI</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>43.22042540958235</v>
+        <v>3.576541080489796</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B11" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>fathmm-XF_coding</t>
+          <t>MutScore</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>42.80940516774943</v>
+        <v>3.558546058805614</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B12" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Eigen-PC-raw_coding</t>
+          <t>REVEL</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>42.59311878423031</v>
+        <v>3.498850938121824</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B13" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MetaLR</t>
+          <t>ClinPred</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>41.80143635914721</v>
+        <v>3.481439562609803</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B14" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C14" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>gMVP</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>38.98051171300805</v>
+        <v>3.452685545653724</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B15" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C15" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>VARITY_R</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>36.18331921105626</v>
+        <v>3.254632073413974</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B16" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C16" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
+          <t>VEST4</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>33.7954747110272</v>
+        <v>3.21020253985234</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B17" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C17" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CADD_raw</t>
+          <t>DEOGEN2</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>30.8313569105263</v>
+        <v>3.196613948015737</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B18" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C18" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MetaSVM</t>
+          <t>VARITY_R_LOO</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>28.92731404548947</v>
+        <v>3.190235109614854</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B19" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C19" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SIFT4G</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>27.50314752751326</v>
+        <v>3.177224026522402</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B20" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C20" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SIFT</t>
+          <t>VARITY_ER_LOO</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>26.55242447380517</v>
+        <v>3.067765074180247</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>553</v>
+        <v>3664</v>
       </c>
       <c r="B21" t="n">
-        <v>427</v>
+        <v>2345</v>
       </c>
       <c r="C21" t="n">
-        <v>126</v>
+        <v>1319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>VARITY_ER</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3.060124203254949</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3664</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2345</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1319</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MetaLR</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2.900170072278002</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3664</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2345</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1319</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AlphaMissense</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2.834097486314746</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3664</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2345</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1319</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SIFT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2.673307451878022</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3664</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2345</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1319</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Polyphen2_HVAR</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2.668050796604022</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3664</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2345</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1319</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Polyphen2_HDIV</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2.568593254620752</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3664</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2345</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1319</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ESM1b</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2.31849693049861</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3664</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2345</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1319</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>MetaSVM</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2.267050616924293</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3664</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2345</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1319</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PROVEAN</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2.175927286480468</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3664</v>
+      </c>
+      <c r="B30" t="n">
+        <v>2345</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1319</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>fathmm-XF_coding</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2.098032865750032</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3664</v>
+      </c>
+      <c r="B31" t="n">
+        <v>2345</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1319</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LIST-S2</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1.81390122646564</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3664</v>
+      </c>
+      <c r="B32" t="n">
+        <v>2345</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1319</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SIFT4G</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1.643955440619929</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3664</v>
+      </c>
+      <c r="B33" t="n">
+        <v>2345</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1319</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>DANN</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>17.6167952865155</v>
+      <c r="E33" t="n">
+        <v>1.575393937207679</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3664</v>
+      </c>
+      <c r="B34" t="n">
+        <v>2345</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1319</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>M-CAP</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1.073989771624617</v>
       </c>
     </row>
   </sheetData>
@@ -3003,13 +2977,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B2" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C2" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3017,56 +2991,56 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4.671893869503933</v>
+        <v>3.972762990620381</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B3" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C3" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CADD_raw</t>
+          <t>BayesDel_noAF</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4.46492974877247</v>
+        <v>3.761388199459161</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B4" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C4" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BayesDel_noAF</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4.276840084145703</v>
+        <v>3.690467746061385</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B5" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C5" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3074,18 +3048,18 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4.192636285038138</v>
+        <v>3.441155779795328</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B6" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C6" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3093,18 +3067,18 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.087919008248451</v>
+        <v>3.373178140711961</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B7" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C7" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3112,18 +3086,18 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3.803459535838075</v>
+        <v>3.070641382271118</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B8" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C8" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3131,151 +3105,151 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3.681327619798411</v>
+        <v>3.060168023423388</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B9" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C9" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PHACTboost</t>
+          <t>REVEL</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3.586334924503044</v>
+        <v>2.92635950499846</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B10" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C10" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>PHACTboost</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3.576541080489796</v>
+        <v>2.877470651636866</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B11" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C11" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MutScore</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3.558546058805614</v>
+        <v>2.871273355112667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B12" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C12" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>REVEL</t>
+          <t>gMVP</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3.498850938121824</v>
+        <v>2.798865437491096</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B13" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C13" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ClinPred</t>
+          <t>MutScore</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3.481439562609803</v>
+        <v>2.779815215441601</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B14" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C14" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>gMVP</t>
+          <t>PrimateAI</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3.452685545653724</v>
+        <v>2.752852142597097</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B15" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C15" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VARITY_R</t>
+          <t>ClinPred</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3.254632073413974</v>
+        <v>2.73148493201596</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B16" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C16" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3283,94 +3257,94 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3.21020253985234</v>
+        <v>2.592774958670413</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B17" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C17" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DEOGEN2</t>
+          <t>MetaLR</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3.196613948015737</v>
+        <v>2.58604628200508</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B18" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C18" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VARITY_R_LOO</t>
+          <t>DEOGEN2</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3.190235109614854</v>
+        <v>2.533897806759644</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B19" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C19" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>VARITY_R</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3.177224026522402</v>
+        <v>2.520755860690078</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B20" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C20" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VARITY_ER_LOO</t>
+          <t>VARITY_R_LOO</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3.067765074180247</v>
+        <v>2.4671769817541</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B21" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C21" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3378,37 +3352,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.060124203254949</v>
+        <v>2.367027437424946</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B22" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C22" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MetaLR</t>
+          <t>VARITY_ER_LOO</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2.900170072278002</v>
+        <v>2.362074198536038</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B23" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C23" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3416,18 +3390,18 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.834097486314746</v>
+        <v>2.104073854084168</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B24" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C24" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3435,18 +3409,18 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.673307451878022</v>
+        <v>2.098143473477988</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B25" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C25" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3454,18 +3428,18 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.668050796604022</v>
+        <v>2.000924605685648</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B26" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C26" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3473,94 +3447,94 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.568593254620752</v>
+        <v>1.906469277428581</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B27" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C27" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ESM1b</t>
+          <t>MetaSVM</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.31849693049861</v>
+        <v>1.902462953307768</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B28" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C28" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MetaSVM</t>
+          <t>ESM1b</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.267050616924293</v>
+        <v>1.84632011194954</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B29" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C29" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>fathmm-XF_coding</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.175927286480468</v>
+        <v>1.676428683235981</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B30" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C30" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>fathmm-XF_coding</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.098032865750032</v>
+        <v>1.670073970138304</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B31" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C31" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3568,18 +3542,18 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.81390122646564</v>
+        <v>1.287180969144706</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B32" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C32" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3587,18 +3561,18 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.643955440619929</v>
+        <v>1.237919231950469</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B33" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C33" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3606,18 +3580,18 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.575393937207679</v>
+        <v>1.134281149624261</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3664</v>
+        <v>3587</v>
       </c>
       <c r="B34" t="n">
-        <v>2345</v>
+        <v>2289</v>
       </c>
       <c r="C34" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3625,7 +3599,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.073989771624617</v>
+        <v>0.8245855167692456</v>
       </c>
     </row>
   </sheetData>
@@ -3671,70 +3645,70 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B2" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C2" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MutFormer</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3.972762990620381</v>
+        <v>3.841083489492484</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B3" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C3" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BayesDel_noAF</t>
+          <t>VEST4</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3.761388199459161</v>
+        <v>3.123192572040083</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B4" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C4" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CADD_raw</t>
+          <t>Polyphen2_HDIV</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3.690467746061385</v>
+        <v>2.637460165303055</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B5" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C5" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3742,558 +3716,558 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3.441155779795328</v>
+        <v>2.526148875395515</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B6" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C6" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Eigen-PC-raw_coding</t>
+          <t>REVEL</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3.373178140711961</v>
+        <v>2.485199058091442</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B7" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C7" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MetaRNN</t>
+          <t>BayesDel_noAF</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3.070641382271118</v>
+        <v>2.480545802534895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B8" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C8" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BayesDel_addAF</t>
+          <t>MetaRNN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3.060168023423388</v>
+        <v>2.447086900319483</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B9" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C9" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>REVEL</t>
+          <t>Polyphen2_HVAR</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.92635950499846</v>
+        <v>2.435763425817508</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B10" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C10" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PHACTboost</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2.877470651636866</v>
+        <v>2.210449977928362</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B11" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C11" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>MetaLR</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2.871273355112667</v>
+        <v>2.179762970712742</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B12" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C12" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>gMVP</t>
+          <t>BayesDel_addAF</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.798865437491096</v>
+        <v>2.102540023409192</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B13" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C13" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MutScore</t>
+          <t>gMVP</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.779815215441601</v>
+        <v>2.095191250535508</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B14" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C14" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>DEOGEN2</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.752852142597097</v>
+        <v>2.003555218624923</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B15" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C15" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ClinPred</t>
+          <t>VARITY_R</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2.73148493201596</v>
+        <v>2.002639520131094</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B16" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C16" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VEST4</t>
+          <t>VARITY_R_LOO</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.592774958670413</v>
+        <v>1.976792597369825</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B17" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C17" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MetaLR</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.58604628200508</v>
+        <v>1.941826997704257</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B18" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C18" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DEOGEN2</t>
+          <t>PHACTboost</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.533897806759644</v>
+        <v>1.90472765538045</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B19" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C19" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VARITY_R</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.520755860690078</v>
+        <v>1.90047101695346</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B20" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C20" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VARITY_R_LOO</t>
+          <t>ClinPred</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2.4671769817541</v>
+        <v>1.819758951637259</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B21" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C21" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VARITY_ER</t>
+          <t>ESM1b</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2.367027437424946</v>
+        <v>1.812812786241814</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B22" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C22" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VARITY_ER_LOO</t>
+          <t>VARITY_ER</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2.362074198536038</v>
+        <v>1.768305376323045</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B23" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C23" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AlphaMissense</t>
+          <t>VARITY_ER_LOO</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.104073854084168</v>
+        <v>1.768222130256009</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B24" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C24" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SIFT</t>
+          <t>PrimateAI</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.098143473477988</v>
+        <v>1.720160067089531</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B25" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C25" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>SIFT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.000924605685648</v>
+        <v>1.695374189246225</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B26" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C26" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
+          <t>MetaSVM</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.906469277428581</v>
+        <v>1.658267499654418</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B27" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C27" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MetaSVM</t>
+          <t>MutFormer</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.902462953307768</v>
+        <v>1.522875991164117</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B28" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C28" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ESM1b</t>
+          <t>MutScore</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.84632011194954</v>
+        <v>1.507382798996169</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B29" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C29" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>fathmm-XF_coding</t>
+          <t>AlphaMissense</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.676428683235981</v>
+        <v>1.245040295236683</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B30" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C30" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>DANN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.670073970138304</v>
+        <v>1.181968435886871</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B31" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C31" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>SIFT4G</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.287180969144706</v>
+        <v>1.106993496945379</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B32" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C32" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SIFT4G</t>
+          <t>M-CAP</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.237919231950469</v>
+        <v>1.086880019884149</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B33" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C33" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DANN</t>
+          <t>LIST-S2</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.134281149624261</v>
+        <v>0.756530024169299</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3587</v>
+        <v>2792</v>
       </c>
       <c r="B34" t="n">
-        <v>2289</v>
+        <v>1458</v>
       </c>
       <c r="C34" t="n">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>M-CAP</t>
+          <t>fathmm-XF_coding</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.8245855167692456</v>
+        <v>0.7069056946445047</v>
       </c>
     </row>
   </sheetData>
@@ -4339,13 +4313,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B2" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C2" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4353,18 +4327,18 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3.841083489492484</v>
+        <v>3.253510073676206</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B3" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C3" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4372,18 +4346,18 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3.123192572040083</v>
+        <v>2.28351560567495</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B4" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C4" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4391,455 +4365,455 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2.637460165303055</v>
+        <v>2.149241262843805</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B5" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C5" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Eigen-raw_coding</t>
+          <t>BayesDel_noAF</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2.526148875395515</v>
+        <v>1.948315360575388</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B6" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C6" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>REVEL</t>
+          <t>Polyphen2_HVAR</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2.485199058091442</v>
+        <v>1.943341061987073</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B7" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C7" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BayesDel_noAF</t>
+          <t>Eigen-raw_coding</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2.480545802534895</v>
+        <v>1.930182930683504</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B8" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C8" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MetaRNN</t>
+          <t>REVEL</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.447086900319483</v>
+        <v>1.912439863863944</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B9" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C9" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>MetaLR</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.435763425817508</v>
+        <v>1.769845425904275</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B10" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C10" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Eigen-PC-raw_coding</t>
+          <t>MetaRNN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2.210449977928362</v>
+        <v>1.67586991938133</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B11" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C11" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MetaLR</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2.179762970712742</v>
+        <v>1.663147141426296</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B12" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C12" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BayesDel_addAF</t>
+          <t>gMVP</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.102540023409192</v>
+        <v>1.530293898522715</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B13" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C13" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>gMVP</t>
+          <t>BayesDel_addAF</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.095191250535508</v>
+        <v>1.498465967197765</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B14" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C14" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DEOGEN2</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.003555218624923</v>
+        <v>1.420654244219652</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B15" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C15" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VARITY_R</t>
+          <t>DEOGEN2</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2.002639520131094</v>
+        <v>1.413904043759981</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B16" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C16" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VARITY_R_LOO</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.976792597369825</v>
+        <v>1.374618252144589</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B17" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C17" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CADD_raw</t>
+          <t>ESM1b</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.941826997704257</v>
+        <v>1.363828853753743</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B18" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C18" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PHACTboost</t>
+          <t>VARITY_R</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.90472765538045</v>
+        <v>1.350485819040653</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B19" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C19" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>VARITY_R_LOO</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.90047101695346</v>
+        <v>1.343726160366086</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B20" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C20" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ClinPred</t>
+          <t>SIFT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.819758951637259</v>
+        <v>1.342629824727362</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B21" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C21" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ESM1b</t>
+          <t>PHACTboost</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.812812786241814</v>
+        <v>1.253757146062676</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B22" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C22" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VARITY_ER</t>
+          <t>MetaSVM</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.768305376323045</v>
+        <v>1.225007439635873</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B23" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C23" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VARITY_ER_LOO</t>
+          <t>ClinPred</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.768222130256009</v>
+        <v>1.211843227006163</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B24" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C24" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>VARITY_ER</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.720160067089531</v>
+        <v>1.189780453661998</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B25" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C25" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SIFT</t>
+          <t>VARITY_ER_LOO</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.695374189246225</v>
+        <v>1.182367875041031</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B26" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C26" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MetaSVM</t>
+          <t>MutFormer</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.658267499654418</v>
+        <v>1.139416287841583</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B27" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C27" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MutFormer</t>
+          <t>PrimateAI</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.522875991164117</v>
+        <v>1.130640991679988</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B28" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C28" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4847,94 +4821,94 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.507382798996169</v>
+        <v>0.9636989466452401</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B29" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C29" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AlphaMissense</t>
+          <t>DANN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.245040295236683</v>
+        <v>0.9386224549018451</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B30" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C30" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DANN</t>
+          <t>SIFT4G</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.181968435886871</v>
+        <v>0.8376062999970291</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B31" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C31" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SIFT4G</t>
+          <t>M-CAP</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.106993496945379</v>
+        <v>0.7370724920068858</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B32" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C32" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>M-CAP</t>
+          <t>AlphaMissense</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.086880019884149</v>
+        <v>0.7352270216879694</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B33" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C33" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4942,18 +4916,18 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.756530024169299</v>
+        <v>0.478972151555717</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2792</v>
+        <v>2741</v>
       </c>
       <c r="B34" t="n">
-        <v>1458</v>
+        <v>1428</v>
       </c>
       <c r="C34" t="n">
-        <v>1334</v>
+        <v>1313</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4961,7 +4935,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.7069056946445047</v>
+        <v>0.3854323976871896</v>
       </c>
     </row>
   </sheetData>
@@ -5007,469 +4981,469 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B2" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C2" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>gMVP</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3.253510073676206</v>
+        <v>22.57257098180227</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B3" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C3" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VEST4</t>
+          <t>PrimateAI</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2.28351560567495</v>
+        <v>22.41207889034278</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B4" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C4" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
+          <t>BayesDel_noAF</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2.149241262843805</v>
+        <v>21.32433667532672</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B5" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C5" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BayesDel_noAF</t>
+          <t>REVEL</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.948315360575388</v>
+        <v>20.40941566266629</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B6" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C6" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>PHACTboost</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.943341061987073</v>
+        <v>20.25960050058347</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B7" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C7" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Eigen-raw_coding</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.930182930683504</v>
+        <v>19.57832771086936</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B8" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C8" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>REVEL</t>
+          <t>AlphaMissense</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.912439863863944</v>
+        <v>18.90929146424813</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B9" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C9" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MetaLR</t>
+          <t>BayesDel_addAF</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.769845425904275</v>
+        <v>18.77932195064596</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B10" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C10" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MetaRNN</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.67586991938133</v>
+        <v>18.1238742201912</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B11" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C11" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Eigen-PC-raw_coding</t>
+          <t>Eigen-raw_coding</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.663147141426296</v>
+        <v>17.85138318887413</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B12" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C12" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>gMVP</t>
+          <t>VARITY_R</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.530293898522715</v>
+        <v>17.83259386558926</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B13" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C13" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BayesDel_addAF</t>
+          <t>MetaRNN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.498465967197765</v>
+        <v>17.75678510113035</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B14" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C14" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CADD_raw</t>
+          <t>MutScore</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.420654244219652</v>
+        <v>17.70836680884606</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B15" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C15" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DEOGEN2</t>
+          <t>VARITY_R_LOO</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.413904043759981</v>
+        <v>17.66529061018321</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B16" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C16" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>VEST4</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.374618252144589</v>
+        <v>17.36688684365831</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B17" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C17" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ESM1b</t>
+          <t>VARITY_ER</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.363828853753743</v>
+        <v>17.03354754039931</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B18" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C18" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VARITY_R</t>
+          <t>VARITY_ER_LOO</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.350485819040653</v>
+        <v>17.02598103897277</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B19" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C19" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VARITY_R_LOO</t>
+          <t>DEOGEN2</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.343726160366086</v>
+        <v>16.79941206896624</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B20" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C20" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SIFT</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.342629824727362</v>
+        <v>16.59181953024838</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B21" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C21" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PHACTboost</t>
+          <t>MetaLR</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.253757146062676</v>
+        <v>16.41742409707068</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B22" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C22" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MetaSVM</t>
+          <t>ClinPred</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.225007439635873</v>
+        <v>16.29351848803678</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B23" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C23" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ClinPred</t>
+          <t>M-CAP</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.211843227006163</v>
+        <v>16.20508484713987</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B24" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C24" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VARITY_ER</t>
+          <t>MetaSVM</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.189780453661998</v>
+        <v>15.51037692918308</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B25" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C25" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VARITY_ER_LOO</t>
+          <t>Polyphen2_HVAR</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.182367875041031</v>
+        <v>14.79624326448971</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B26" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C26" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5477,132 +5451,132 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.139416287841583</v>
+        <v>14.73898728898749</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B27" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C27" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>Polyphen2_HDIV</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.130640991679988</v>
+        <v>13.97803727776069</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B28" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C28" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MutScore</t>
+          <t>ESM1b</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9636989466452401</v>
+        <v>13.92593668365968</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B29" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C29" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DANN</t>
+          <t>SIFT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9386224549018451</v>
+        <v>11.67387949158575</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B30" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C30" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SIFT4G</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.8376062999970291</v>
+        <v>10.8618448758867</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B31" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C31" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>M-CAP</t>
+          <t>fathmm-XF_coding</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.7370724920068858</v>
+        <v>10.12471307090331</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B32" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C32" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AlphaMissense</t>
+          <t>SIFT4G</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.7352270216879694</v>
+        <v>9.307514533755594</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B33" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C33" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5610,26 +5584,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.478972151555717</v>
+        <v>8.960160676490048</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2741</v>
+        <v>21620</v>
       </c>
       <c r="B34" t="n">
-        <v>1428</v>
+        <v>20292</v>
       </c>
       <c r="C34" t="n">
-        <v>1313</v>
+        <v>1328</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>fathmm-XF_coding</t>
+          <t>DANN</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.3854323976871896</v>
+        <v>7.96655151010093</v>
       </c>
     </row>
   </sheetData>
@@ -5675,13 +5649,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B2" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C2" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5689,132 +5663,132 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22.57257098180227</v>
+        <v>13.23565867489841</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B3" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C3" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>BayesDel_noAF</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>22.41207889034278</v>
+        <v>13.16841227861262</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B4" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C4" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BayesDel_noAF</t>
+          <t>PrimateAI</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>21.32433667532672</v>
+        <v>12.72191294211427</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B5" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C5" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>REVEL</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20.40941566266629</v>
+        <v>12.57708036544046</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B6" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C6" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PHACTboost</t>
+          <t>REVEL</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>20.25960050058347</v>
+        <v>12.03924695100907</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B7" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C7" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CADD_raw</t>
+          <t>Eigen-raw_coding</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>19.57832771086936</v>
+        <v>11.28146281786298</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B8" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C8" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AlphaMissense</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>18.90929146424813</v>
+        <v>11.04957341891383</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B9" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C9" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5822,284 +5796,284 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>18.77932195064596</v>
+        <v>10.65406828692002</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B10" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C10" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18.1238742201912</v>
+        <v>10.50081571863509</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B11" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C11" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Eigen-raw_coding</t>
+          <t>PHACTboost</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.85138318887413</v>
+        <v>10.39335512540352</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B12" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C12" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VARITY_R</t>
+          <t>MetaRNN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>17.83259386558926</v>
+        <v>10.14348472839791</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B13" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C13" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MetaRNN</t>
+          <t>VEST4</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>17.75678510113035</v>
+        <v>10.14309886569416</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B14" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C14" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MutScore</t>
+          <t>MetaLR</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>17.70836680884606</v>
+        <v>10.08631320938905</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B15" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C15" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VARITY_R_LOO</t>
+          <t>VARITY_R</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>17.66529061018321</v>
+        <v>9.939471136316651</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B16" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C16" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VEST4</t>
+          <t>VARITY_R_LOO</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>17.36688684365831</v>
+        <v>9.901679061268526</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B17" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C17" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VARITY_ER</t>
+          <t>AlphaMissense</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>17.03354754039931</v>
+        <v>9.879707290377466</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B18" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C18" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VARITY_ER_LOO</t>
+          <t>Polyphen2_HVAR</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>17.02598103897277</v>
+        <v>9.434910739447474</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B19" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C19" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DEOGEN2</t>
+          <t>VARITY_ER_LOO</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>16.79941206896624</v>
+        <v>9.428738900654343</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B20" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C20" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Eigen-PC-raw_coding</t>
+          <t>VARITY_ER</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>16.59181953024838</v>
+        <v>9.417156568374581</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B21" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C21" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MetaLR</t>
+          <t>Polyphen2_HDIV</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>16.41742409707068</v>
+        <v>9.224385064053637</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B22" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C22" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ClinPred</t>
+          <t>M-CAP</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>16.29351848803678</v>
+        <v>9.125007358821671</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B23" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C23" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>M-CAP</t>
+          <t>MutScore</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>16.20508484713987</v>
+        <v>9.039997064326963</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B24" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C24" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6107,75 +6081,75 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>15.51037692918308</v>
+        <v>8.982778098354283</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B25" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C25" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>ClinPred</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>14.79624326448971</v>
+        <v>8.951433473045864</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B26" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C26" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MutFormer</t>
+          <t>DEOGEN2</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>14.73898728898749</v>
+        <v>8.727552817313448</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B27" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C27" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
+          <t>MutFormer</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>13.97803727776069</v>
+        <v>7.644666683174607</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B28" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C28" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -6183,18 +6157,18 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>13.92593668365968</v>
+        <v>7.371930135791352</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B29" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C29" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6202,18 +6176,18 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>11.67387949158575</v>
+        <v>6.659613246997512</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B30" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C30" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -6221,18 +6195,18 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>10.8618448758867</v>
+        <v>6.173270934065352</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B31" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C31" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6240,18 +6214,18 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>10.12471307090331</v>
+        <v>5.527219348213816</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B32" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C32" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -6259,45 +6233,45 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>9.307514533755594</v>
+        <v>5.29981164805156</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B33" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C33" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>DANN</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>8.960160676490048</v>
+        <v>5.160588870175516</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>21620</v>
+        <v>20141</v>
       </c>
       <c r="B34" t="n">
-        <v>20292</v>
+        <v>18834</v>
       </c>
       <c r="C34" t="n">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DANN</t>
+          <t>LIST-S2</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>7.96655151010093</v>
+        <v>4.543163361718147</v>
       </c>
     </row>
   </sheetData>
@@ -6311,7 +6285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6343,526 +6317,526 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B2" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C2" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gMVP</t>
+          <t>MutScore</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>13.23565867489841</v>
+        <v>214.4890286852904</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B3" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C3" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BayesDel_noAF</t>
+          <t>VARITY_R</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>13.16841227861262</v>
+        <v>181.9979742959815</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B4" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C4" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>VARITY_R_LOO</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>12.72191294211427</v>
+        <v>179.6004127604759</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B5" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C5" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CADD_raw</t>
+          <t>VARITY_ER</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12.57708036544046</v>
+        <v>177.4912347810603</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B6" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C6" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>REVEL</t>
+          <t>VARITY_ER_LOO</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12.03924695100907</v>
+        <v>175.3089946932058</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B7" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C7" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Eigen-raw_coding</t>
+          <t>PHACTboost</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>11.28146281786298</v>
+        <v>173.2789913160225</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B8" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C8" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>AlphaMissense</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>11.04957341891383</v>
+        <v>168.9730113327543</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B9" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C9" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BayesDel_addAF</t>
+          <t>MetaRNN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.65406828692002</v>
+        <v>154.2861226084239</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B10" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C10" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Eigen-PC-raw_coding</t>
+          <t>REVEL</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10.50081571863509</v>
+        <v>152.0389111344953</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B11" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C11" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PHACTboost</t>
+          <t>BayesDel_addAF</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.39335512540352</v>
+        <v>151.1220133126949</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B12" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C12" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MetaRNN</t>
+          <t>BayesDel_noAF</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.14348472839791</v>
+        <v>143.4268800883658</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B13" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C13" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VEST4</t>
+          <t>DEOGEN2</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>10.14309886569416</v>
+        <v>138.1637198663264</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B14" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C14" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MetaLR</t>
+          <t>gMVP</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>10.08631320938905</v>
+        <v>135.4076990642274</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B15" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C15" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VARITY_R</t>
+          <t>ClinPred</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9.939471136316651</v>
+        <v>130.5752716566966</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B16" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C16" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VARITY_R_LOO</t>
+          <t>VEST4</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>9.901679061268526</v>
+        <v>129.8897651163582</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B17" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C17" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AlphaMissense</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9.879707290377466</v>
+        <v>127.554354072476</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B18" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C18" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>ESM1b</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9.434910739447474</v>
+        <v>121.4058680382153</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B19" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C19" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VARITY_ER_LOO</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.428738900654343</v>
+        <v>116.7664252960993</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B20" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C20" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VARITY_ER</t>
+          <t>M-CAP</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9.417156568374581</v>
+        <v>105.9625441153106</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B21" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C21" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
+          <t>fathmm-XF_coding</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9.224385064053637</v>
+        <v>98.75288900436246</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B22" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C22" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>M-CAP</t>
+          <t>MetaSVM</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>9.125007358821671</v>
+        <v>92.46623318011291</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B23" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C23" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MutScore</t>
+          <t>MetaLR</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>9.039997064326963</v>
+        <v>86.65597022596967</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B24" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C24" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MetaSVM</t>
+          <t>SIFT4G</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>8.982778098354283</v>
+        <v>85.87676158753474</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B25" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C25" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ClinPred</t>
+          <t>PrimateAI</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>8.951433473045864</v>
+        <v>83.13714236249855</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B26" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C26" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DEOGEN2</t>
+          <t>Eigen-raw_coding</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>8.727552817313448</v>
+        <v>81.1638303645538</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B27" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C27" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MutFormer</t>
+          <t>Polyphen2_HVAR</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>7.644666683174607</v>
+        <v>80.53454691712801</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B28" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C28" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ESM1b</t>
+          <t>MutFormer</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>7.371930135791352</v>
+        <v>79.97239771871907</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B29" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C29" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6870,94 +6844,94 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6.659613246997512</v>
+        <v>75.74916823258745</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B30" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C30" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6.173270934065352</v>
+        <v>70.62958015077999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B31" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C31" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>fathmm-XF_coding</t>
+          <t>MutationAssessor</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5.527219348213816</v>
+        <v>69.40989375652327</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B32" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C32" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SIFT4G</t>
+          <t>Polyphen2_HDIV</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5.29981164805156</v>
+        <v>60.62738249851637</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B33" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C33" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DANN</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5.160588870175516</v>
+        <v>60.01541659883077</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>20141</v>
+        <v>5468</v>
       </c>
       <c r="B34" t="n">
-        <v>18834</v>
+        <v>692</v>
       </c>
       <c r="C34" t="n">
-        <v>1307</v>
+        <v>4776</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -6965,7 +6939,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4.543163361718147</v>
+        <v>52.86973038605111</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>5468</v>
+      </c>
+      <c r="B35" t="n">
+        <v>692</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DANN</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>12.11626821896182</v>
       </c>
     </row>
   </sheetData>
@@ -6979,7 +6972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7011,13 +7004,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B2" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C2" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7025,189 +7018,189 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>214.4890286852904</v>
+        <v>245.8904887588197</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B3" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C3" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VARITY_R</t>
+          <t>PHACTboost</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>181.9979742959815</v>
+        <v>245.8728523721136</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B4" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C4" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VARITY_R_LOO</t>
+          <t>DEOGEN2</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>179.6004127604759</v>
+        <v>233.4277665778547</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B5" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C5" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VARITY_ER</t>
+          <t>VARITY_R</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>177.4912347810603</v>
+        <v>212.8967673942211</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B6" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C6" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VARITY_ER_LOO</t>
+          <t>AlphaMissense</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>175.3089946932058</v>
+        <v>212.2788476306537</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B7" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C7" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PHACTboost</t>
+          <t>VARITY_R_LOO</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>173.2789913160225</v>
+        <v>210.6785412436383</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B8" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C8" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AlphaMissense</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>168.9730113327543</v>
+        <v>210.290090002572</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B9" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C9" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MetaRNN</t>
+          <t>MutFormer</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>154.2861226084239</v>
+        <v>203.2388738337594</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B10" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C10" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>REVEL</t>
+          <t>BayesDel_addAF</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>152.0389111344953</v>
+        <v>201.7692548071157</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B11" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C11" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BayesDel_addAF</t>
+          <t>REVEL</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>151.1220133126949</v>
+        <v>200.9577962564772</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B12" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C12" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -7215,444 +7208,425 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>143.4268800883658</v>
+        <v>196.4967626959752</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B13" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C13" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DEOGEN2</t>
+          <t>M-CAP</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>138.1637198663264</v>
+        <v>196.1868048729784</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B14" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C14" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>gMVP</t>
+          <t>VARITY_ER</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135.4076990642274</v>
+        <v>195.7565922016557</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B15" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C15" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ClinPred</t>
+          <t>VARITY_ER_LOO</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>130.5752716566966</v>
+        <v>193.629973792348</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B16" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C16" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VEST4</t>
+          <t>MetaRNN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>129.8897651163582</v>
+        <v>180.4392221054474</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B17" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C17" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>gMVP</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>127.554354072476</v>
+        <v>176.120309981947</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B18" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C18" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ESM1b</t>
+          <t>VEST4</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>121.4058680382153</v>
+        <v>161.8739138338677</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B19" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C19" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>PrimateAI</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>116.7664252960993</v>
+        <v>159.4250702564201</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B20" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C20" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>M-CAP</t>
+          <t>ESM1b</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105.9625441153106</v>
+        <v>145.9647228392468</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B21" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C21" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>fathmm-XF_coding</t>
+          <t>MetaSVM</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>98.75288900436246</v>
+        <v>145.82009431903</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B22" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C22" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MetaSVM</t>
+          <t>MetaLR</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>92.46623318011291</v>
+        <v>143.1746043217669</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B23" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C23" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MetaLR</t>
+          <t>ClinPred</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>86.65597022596967</v>
+        <v>142.5152741785305</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B24" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C24" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SIFT4G</t>
+          <t>fathmm-XF_coding</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>85.87676158753474</v>
+        <v>134.0724394663311</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B25" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C25" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>83.13714236249855</v>
+        <v>114.6547375724535</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B26" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C26" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Eigen-raw_coding</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>81.1638303645538</v>
+        <v>110.0496729351844</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B27" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C27" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>Eigen-raw_coding</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>80.53454691712801</v>
+        <v>108.7778057341493</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B28" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C28" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MutFormer</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>79.97239771871907</v>
+        <v>105.4178802510487</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B29" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C29" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SIFT</t>
+          <t>LIST-S2</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>75.74916823258745</v>
+        <v>101.9992864738806</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B30" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C30" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Eigen-PC-raw_coding</t>
+          <t>Polyphen2_HVAR</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>70.62958015077999</v>
+        <v>92.40553915947402</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B31" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C31" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MutationAssessor</t>
+          <t>SIFT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>69.40989375652327</v>
+        <v>91.84657988937583</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B32" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C32" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
+          <t>SIFT4G</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>60.62738249851637</v>
+        <v>81.2900444831494</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B33" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C33" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CADD_raw</t>
+          <t>Polyphen2_HDIV</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>60.01541659883077</v>
+        <v>78.07559147447023</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>5468</v>
+        <v>4383</v>
       </c>
       <c r="B34" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="C34" t="n">
-        <v>4776</v>
+        <v>3682</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>DANN</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>52.86973038605111</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>5468</v>
-      </c>
-      <c r="B35" t="n">
-        <v>692</v>
-      </c>
-      <c r="C35" t="n">
-        <v>4776</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>DANN</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>12.11626821896182</v>
+        <v>38.25141659992671</v>
       </c>
     </row>
   </sheetData>
@@ -8372,674 +8346,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Variant_Total</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Positive_Labels</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Negative_Labels</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>VEP</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>MWU_neg_log10_pval</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B2" t="n">
-        <v>701</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MutScore</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>245.8904887588197</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B3" t="n">
-        <v>701</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>PHACTboost</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>245.8728523721136</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B4" t="n">
-        <v>701</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>DEOGEN2</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>233.4277665778547</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B5" t="n">
-        <v>701</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VARITY_R</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>212.8967673942211</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B6" t="n">
-        <v>701</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AlphaMissense</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>212.2788476306537</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B7" t="n">
-        <v>701</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>VARITY_R_LOO</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>210.6785412436383</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B8" t="n">
-        <v>701</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>210.290090002572</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B9" t="n">
-        <v>701</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MutFormer</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>203.2388738337594</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B10" t="n">
-        <v>701</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>BayesDel_addAF</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>201.7692548071157</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B11" t="n">
-        <v>701</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>REVEL</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>200.9577962564772</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B12" t="n">
-        <v>701</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>BayesDel_noAF</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>196.4967626959752</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B13" t="n">
-        <v>701</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>M-CAP</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>196.1868048729784</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B14" t="n">
-        <v>701</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>VARITY_ER</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>195.7565922016557</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B15" t="n">
-        <v>701</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>VARITY_ER_LOO</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>193.629973792348</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B16" t="n">
-        <v>701</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>MetaRNN</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>180.4392221054474</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B17" t="n">
-        <v>701</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>gMVP</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>176.120309981947</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B18" t="n">
-        <v>701</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>VEST4</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>161.8739138338677</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B19" t="n">
-        <v>701</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>PrimateAI</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>159.4250702564201</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B20" t="n">
-        <v>701</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ESM1b</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>145.9647228392468</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B21" t="n">
-        <v>701</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>MetaSVM</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>145.82009431903</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B22" t="n">
-        <v>701</v>
-      </c>
-      <c r="C22" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>MetaLR</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>143.1746043217669</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B23" t="n">
-        <v>701</v>
-      </c>
-      <c r="C23" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>ClinPred</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>142.5152741785305</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B24" t="n">
-        <v>701</v>
-      </c>
-      <c r="C24" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>fathmm-XF_coding</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>134.0724394663311</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B25" t="n">
-        <v>701</v>
-      </c>
-      <c r="C25" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>PROVEAN</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>114.6547375724535</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B26" t="n">
-        <v>701</v>
-      </c>
-      <c r="C26" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>CADD_raw</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>110.0496729351844</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B27" t="n">
-        <v>701</v>
-      </c>
-      <c r="C27" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Eigen-raw_coding</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>108.7778057341493</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B28" t="n">
-        <v>701</v>
-      </c>
-      <c r="C28" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Eigen-PC-raw_coding</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>105.4178802510487</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B29" t="n">
-        <v>701</v>
-      </c>
-      <c r="C29" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>LIST-S2</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>101.9992864738806</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B30" t="n">
-        <v>701</v>
-      </c>
-      <c r="C30" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Polyphen2_HVAR</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>92.40553915947402</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B31" t="n">
-        <v>701</v>
-      </c>
-      <c r="C31" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>SIFT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>91.84657988937583</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B32" t="n">
-        <v>701</v>
-      </c>
-      <c r="C32" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>SIFT4G</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>81.2900444831494</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B33" t="n">
-        <v>701</v>
-      </c>
-      <c r="C33" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Polyphen2_HDIV</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>78.07559147447023</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>4383</v>
-      </c>
-      <c r="B34" t="n">
-        <v>701</v>
-      </c>
-      <c r="C34" t="n">
-        <v>3682</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>DANN</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>38.25141659992671</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -9714,362 +9020,6 @@
       </c>
       <c r="E35" t="n">
         <v>51.02825481657639</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Variant_Total</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Positive_Labels</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Negative_Labels</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>VEP</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>MWU_neg_log10_pval</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>35119</v>
-      </c>
-      <c r="B2" t="n">
-        <v>18953</v>
-      </c>
-      <c r="C2" t="n">
-        <v>16166</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>AlphaMissense</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>35119</v>
-      </c>
-      <c r="B3" t="n">
-        <v>18953</v>
-      </c>
-      <c r="C3" t="n">
-        <v>16166</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>BayesDel_addAF</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>35119</v>
-      </c>
-      <c r="B4" t="n">
-        <v>18953</v>
-      </c>
-      <c r="C4" t="n">
-        <v>16166</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>BayesDel_noAF</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>35119</v>
-      </c>
-      <c r="B5" t="n">
-        <v>18953</v>
-      </c>
-      <c r="C5" t="n">
-        <v>16166</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ClinPred</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>35119</v>
-      </c>
-      <c r="B6" t="n">
-        <v>18953</v>
-      </c>
-      <c r="C6" t="n">
-        <v>16166</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>DANN</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>35119</v>
-      </c>
-      <c r="B7" t="n">
-        <v>18953</v>
-      </c>
-      <c r="C7" t="n">
-        <v>16166</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>DEOGEN2</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>35119</v>
-      </c>
-      <c r="B8" t="n">
-        <v>18953</v>
-      </c>
-      <c r="C8" t="n">
-        <v>16166</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ESM1b</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>35119</v>
-      </c>
-      <c r="B9" t="n">
-        <v>18953</v>
-      </c>
-      <c r="C9" t="n">
-        <v>16166</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LIST-S2</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>35119</v>
-      </c>
-      <c r="B10" t="n">
-        <v>18953</v>
-      </c>
-      <c r="C10" t="n">
-        <v>16166</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>MetaLR</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>35119</v>
-      </c>
-      <c r="B11" t="n">
-        <v>18953</v>
-      </c>
-      <c r="C11" t="n">
-        <v>16166</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>MetaRNN</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>35119</v>
-      </c>
-      <c r="B12" t="n">
-        <v>18953</v>
-      </c>
-      <c r="C12" t="n">
-        <v>16166</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>MetaSVM</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>35119</v>
-      </c>
-      <c r="B13" t="n">
-        <v>18953</v>
-      </c>
-      <c r="C13" t="n">
-        <v>16166</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>MutFormer</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>35119</v>
-      </c>
-      <c r="B14" t="n">
-        <v>18953</v>
-      </c>
-      <c r="C14" t="n">
-        <v>16166</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>MutScore</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>35119</v>
-      </c>
-      <c r="B15" t="n">
-        <v>18953</v>
-      </c>
-      <c r="C15" t="n">
-        <v>16166</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>REVEL</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>35119</v>
-      </c>
-      <c r="B16" t="n">
-        <v>18953</v>
-      </c>
-      <c r="C16" t="n">
-        <v>16166</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>VEST4</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/curation_benchmark/results/supp_tables/supp_table_MWU.xlsx
+++ b/curation_benchmark/results/supp_tables/supp_table_MWU.xlsx
@@ -1,32 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ADRD (80%)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ASD (80%)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ASD_excl_ClinVar (80%)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CHD (80%)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="CHD_excl_ClinVar (80%)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="DDD (80%)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="DDD_excl_ClinVar (80%)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Cancer_MSK (80%)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Cancer_TCGA (80%)" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Cancer_AlphaMissense (80%)" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ADRD (90%)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="ASD (90%)" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="ASD_excl_ClinVar (90%)" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="CHD (90%)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="CHD_excl_ClinVar (90%)" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="DDD (90%)" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="DDD_excl_ClinVar (90%)" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Cancer_MSK (90%)" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Cancer_TCGA (90%)" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Cancer_AlphaMissense (90%)" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADRD (80%)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASD (80%)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASD_excl_ClinVar (80%)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHD (80%)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHD_excl_ClinVar (80%)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDD (80%)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDD_excl_ClinVar (80%)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancer_MSK (80%)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancer_TCGA (80%)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancer_AlphaMissense (80%)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADRD (90%)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASD (90%)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASD_excl_ClinVar (90%)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHD (90%)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHD_excl_ClinVar (90%)" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDD (90%)" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDD_excl_ClinVar (90%)" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancer_MSK (90%)" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancer_TCGA (90%)" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancer_AlphaMissense (90%)" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
